--- a/monitor_xlsx/20260309.xlsx
+++ b/monitor_xlsx/20260309.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2213,6 +2213,165 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>962</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>826</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>-116</v>
+      </c>
+      <c r="G21" t="n">
+        <v>217</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>16</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-53</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>624</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2549</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>307</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-95</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-191</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-329</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-9.82</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2004</v>
+      </c>
+      <c r="H23" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" t="n">
+        <v>442</v>
+      </c>
+      <c r="J23" t="n">
+        <v>101</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3283</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14568</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-106287</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260309.xlsx
+++ b/monitor_xlsx/20260309.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2372,6 +2372,59 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6359</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1145</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1281</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>477</v>
+      </c>
+      <c r="J24" t="n">
+        <v>415</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6738</v>
+      </c>
+      <c r="L24" t="n">
+        <v>34458</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-58901</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
